--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_09-09-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_09-09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4C4678-67DF-43C7-8E5E-99A2464173E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1757F7B3-A0DB-45A4-9DCA-54EB03E9813C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="1635" windowWidth="21600" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30975" yWindow="1470" windowWidth="21600" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -469,12 +469,6 @@
     <t>£69.02</t>
   </si>
   <si>
-    <t>£141.19</t>
-  </si>
-  <si>
-    <t>£143.21</t>
-  </si>
-  <si>
     <t>£678.81</t>
   </si>
   <si>
@@ -529,9 +523,6 @@
     <t>£659.55</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.tradeinsulations.co.uk/product/140mm-recticel-eurowall-plus/</t>
-  </si>
-  <si>
     <t>£14.76</t>
   </si>
   <si>
@@ -788,6 +779,15 @@
   </si>
   <si>
     <t>£56.50</t>
+  </si>
+  <si>
+    <t>£705.95</t>
+  </si>
+  <si>
+    <t>£716.05</t>
+  </si>
+  <si>
+    <t>£559.96</t>
   </si>
 </sst>
 </file>
@@ -1231,7 +1231,7 @@
         <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G2" t="s">
         <v>89</v>
@@ -1252,22 +1252,22 @@
         <v>88</v>
       </c>
       <c r="M2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="N2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P2" t="s">
         <v>117</v>
       </c>
       <c r="Q2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="R2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1287,7 +1287,7 @@
         <v>67</v>
       </c>
       <c r="F3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G3" t="s">
         <v>67</v>
@@ -1308,22 +1308,22 @@
         <v>88</v>
       </c>
       <c r="M3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="N3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P3" t="s">
         <v>117</v>
       </c>
       <c r="Q3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="R3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1343,7 +1343,7 @@
         <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G4" t="s">
         <v>68</v>
@@ -1364,22 +1364,22 @@
         <v>88</v>
       </c>
       <c r="M4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="N4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="O4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P4" t="s">
         <v>117</v>
       </c>
       <c r="Q4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="R4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1420,22 +1420,22 @@
         <v>88</v>
       </c>
       <c r="M5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="O5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P5" t="s">
         <v>117</v>
       </c>
       <c r="Q5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="R5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1455,7 +1455,7 @@
         <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G6" t="s">
         <v>70</v>
@@ -1467,7 +1467,7 @@
         <v>116</v>
       </c>
       <c r="J6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K6" t="s">
         <v>140</v>
@@ -1476,22 +1476,22 @@
         <v>88</v>
       </c>
       <c r="M6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P6" t="s">
         <v>117</v>
       </c>
       <c r="Q6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="R6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1511,7 +1511,7 @@
         <v>71</v>
       </c>
       <c r="F7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G7" t="s">
         <v>71</v>
@@ -1520,7 +1520,7 @@
         <v>100</v>
       </c>
       <c r="I7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J7" t="s">
         <v>131</v>
@@ -1532,22 +1532,22 @@
         <v>88</v>
       </c>
       <c r="M7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="N7" t="s">
         <v>117</v>
       </c>
       <c r="O7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P7" t="s">
         <v>117</v>
       </c>
       <c r="Q7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="R7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1567,7 +1567,7 @@
         <v>72</v>
       </c>
       <c r="F8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G8" t="s">
         <v>72</v>
@@ -1588,10 +1588,10 @@
         <v>88</v>
       </c>
       <c r="M8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="N8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O8" t="s">
         <v>100</v>
@@ -1600,10 +1600,10 @@
         <v>117</v>
       </c>
       <c r="Q8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="R8" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1623,7 +1623,7 @@
         <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G9" t="s">
         <v>73</v>
@@ -1635,7 +1635,7 @@
         <v>119</v>
       </c>
       <c r="J9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K9" t="s">
         <v>143</v>
@@ -1644,22 +1644,22 @@
         <v>88</v>
       </c>
       <c r="M9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="N9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P9" t="s">
         <v>117</v>
       </c>
       <c r="Q9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="R9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1691,7 +1691,7 @@
         <v>120</v>
       </c>
       <c r="J10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="K10" t="s">
         <v>143</v>
@@ -1706,7 +1706,7 @@
         <v>117</v>
       </c>
       <c r="O10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="P10" t="s">
         <v>117</v>
@@ -1715,7 +1715,7 @@
         <v>75</v>
       </c>
       <c r="R10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1735,7 +1735,7 @@
         <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G11" t="s">
         <v>75</v>
@@ -1756,22 +1756,22 @@
         <v>88</v>
       </c>
       <c r="M11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N11" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="O11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P11" t="s">
         <v>117</v>
       </c>
       <c r="Q11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="R11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1791,7 +1791,7 @@
         <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G12" t="s">
         <v>76</v>
@@ -1812,19 +1812,19 @@
         <v>88</v>
       </c>
       <c r="M12" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N12" t="s">
         <v>117</v>
       </c>
       <c r="O12" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P12" t="s">
         <v>117</v>
       </c>
       <c r="Q12" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="R12" t="s">
         <v>88</v>
@@ -1847,7 +1847,7 @@
         <v>77</v>
       </c>
       <c r="F13" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G13" t="s">
         <v>77</v>
@@ -1859,7 +1859,7 @@
         <v>123</v>
       </c>
       <c r="J13" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="K13" t="s">
         <v>145</v>
@@ -1868,22 +1868,22 @@
         <v>88</v>
       </c>
       <c r="M13" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="N13" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O13" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P13" t="s">
         <v>117</v>
       </c>
       <c r="Q13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="R13" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1903,7 +1903,7 @@
         <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G14" t="s">
         <v>78</v>
@@ -1915,7 +1915,7 @@
         <v>124</v>
       </c>
       <c r="J14" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="K14" t="s">
         <v>146</v>
@@ -1924,19 +1924,19 @@
         <v>88</v>
       </c>
       <c r="M14" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P14" t="s">
         <v>117</v>
       </c>
       <c r="Q14" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R14" t="s">
         <v>88</v>
@@ -1959,7 +1959,7 @@
         <v>88</v>
       </c>
       <c r="F15" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G15" t="s">
         <v>79</v>
@@ -1980,19 +1980,19 @@
         <v>88</v>
       </c>
       <c r="M15" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N15" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P15" t="s">
         <v>117</v>
       </c>
       <c r="Q15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="R15" t="s">
         <v>88</v>
@@ -2015,7 +2015,7 @@
         <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G16" t="s">
         <v>80</v>
@@ -2027,7 +2027,7 @@
         <v>126</v>
       </c>
       <c r="J16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="K16" t="s">
         <v>148</v>
@@ -2036,22 +2036,22 @@
         <v>88</v>
       </c>
       <c r="M16" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N16" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O16" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P16" t="s">
         <v>117</v>
       </c>
       <c r="Q16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="R16" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2062,10 +2062,10 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D17" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E17" t="s">
         <v>88</v>
@@ -2139,7 +2139,7 @@
         <v>88</v>
       </c>
       <c r="J18" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="K18" t="s">
         <v>88</v>
@@ -2151,10 +2151,10 @@
         <v>88</v>
       </c>
       <c r="N18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O18" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P18" t="s">
         <v>117</v>
@@ -2195,7 +2195,7 @@
         <v>88</v>
       </c>
       <c r="J19" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="K19" t="s">
         <v>88</v>
@@ -2207,10 +2207,10 @@
         <v>88</v>
       </c>
       <c r="N19" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="P19" t="s">
         <v>117</v>
@@ -2219,7 +2219,7 @@
         <v>88</v>
       </c>
       <c r="R19" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2307,7 +2307,7 @@
         <v>88</v>
       </c>
       <c r="J21" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="K21" t="s">
         <v>88</v>
@@ -2363,7 +2363,7 @@
         <v>88</v>
       </c>
       <c r="J22" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="K22" t="s">
         <v>88</v>
@@ -2422,19 +2422,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s">
-        <v>149</v>
+        <v>253</v>
       </c>
       <c r="L23" t="s">
         <v>88</v>
       </c>
       <c r="M23" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N23" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O23" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P23" t="s">
         <v>88</v>
@@ -2443,7 +2443,7 @@
         <v>88</v>
       </c>
       <c r="R23" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2478,7 +2478,7 @@
         <v>88</v>
       </c>
       <c r="K24" t="s">
-        <v>150</v>
+        <v>254</v>
       </c>
       <c r="L24" t="s">
         <v>88</v>
@@ -2487,10 +2487,10 @@
         <v>117</v>
       </c>
       <c r="N24" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P24" t="s">
         <v>88</v>
@@ -2499,7 +2499,7 @@
         <v>88</v>
       </c>
       <c r="R24" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2534,7 +2534,7 @@
         <v>88</v>
       </c>
       <c r="K25" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L25" t="s">
         <v>88</v>
@@ -2543,10 +2543,10 @@
         <v>117</v>
       </c>
       <c r="N25" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O25" t="s">
-        <v>169</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s">
         <v>88</v>
@@ -2555,7 +2555,7 @@
         <v>88</v>
       </c>
       <c r="R25" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
